--- a/AAII_Financials/Quarterly/ITOCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ITOCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>ITOCY</t>
   </si>
@@ -656,72 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44286</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -758,8 +761,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -796,8 +802,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -834,8 +843,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,8 +862,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -888,8 +901,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,8 +942,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -964,8 +983,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1002,8 +1024,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,8 +1040,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1053,8 +1079,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1091,8 +1120,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,8 +1139,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1145,8 +1178,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1183,8 +1219,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1221,8 +1260,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1259,8 +1301,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1297,8 +1342,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,8 +1383,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1373,8 +1424,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1411,8 +1465,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1547,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,8 +1629,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1601,8 +1670,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1639,8 +1711,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,8 +1752,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1715,51 +1793,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44286</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,350 +1875,378 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3734300</v>
+      </c>
+      <c r="E41" s="3">
         <v>3702000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3670000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3710200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3969700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4558700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5037400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4918800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4061200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4271800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4558700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4029200</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1306200</v>
+      </c>
+      <c r="E42" s="3">
         <v>597500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>583200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>794400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>586000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>622900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>931500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>496200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>729100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>759000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>622900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>852800</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20257200</v>
+      </c>
+      <c r="E43" s="3">
         <v>21518800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20152600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20517100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20003100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20325100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21506600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20283100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21026800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19978000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20325100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23554900</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9715400</v>
+      </c>
+      <c r="E44" s="3">
         <v>10690300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9898900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9176700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9138000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9816500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8870300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8125700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9065500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9042000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9816500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11183100</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4420200</v>
+      </c>
+      <c r="E45" s="3">
         <v>3910000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3918200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3261700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3483900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3202500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3263800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4850400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2770300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2743800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3202500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2929600</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>39433300</v>
+      </c>
+      <c r="E46" s="3">
         <v>40418700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38222900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37460100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37180600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38525600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39609600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38674000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37652900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36794600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38525600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>42549500</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34608200</v>
+      </c>
+      <c r="E47" s="3">
         <v>32472900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>31498300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28220600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>28776700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28375900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26738600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>25498900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>27968100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>27639400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28375900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28232800</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15200100</v>
+      </c>
+      <c r="E48" s="3">
         <v>15403600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14901000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13412900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13954000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15033700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15943200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17539000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13606600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13909500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15033700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15201700</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7725700</v>
+      </c>
+      <c r="E49" s="3">
         <v>8420000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8076200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7086000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7459600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8118700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8907000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10179400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7386900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7614300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8118700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8526600</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,46 +2324,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1991100</v>
+      </c>
+      <c r="E52" s="3">
         <v>8055000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1949600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7723200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2038600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2183900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2611600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2750800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7842900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8013100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2183900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8230600</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2406,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>105234500</v>
+      </c>
+      <c r="E54" s="3">
         <v>105201800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>101064900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>94309600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>95796500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>98661000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>100084500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>101071700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>94868100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94355500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>98661000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>103123200</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,236 +2483,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15107600</v>
+      </c>
+      <c r="E57" s="3">
         <v>16081800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15108400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15625600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15491100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15365600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16199100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14726800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16249100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14709300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15365600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18650700</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6221400</v>
+      </c>
+      <c r="E58" s="3">
         <v>7236000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7094900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6503200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6294400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6755200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6244000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8577500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6504600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6807200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6755200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7089700</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8632900</v>
+      </c>
+      <c r="E59" s="3">
         <v>8090000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7757600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6830700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6923500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7554300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7618900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8835600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6719800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6930700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7554300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7801500</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29961900</v>
+      </c>
+      <c r="E60" s="3">
         <v>31407900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29960900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28959500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28709000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29675100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30062000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32139800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29473400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28447100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29675100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33542000</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23702600</v>
+      </c>
+      <c r="E61" s="3">
         <v>24759200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23768300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>21690000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22770400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23419200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26011100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>29568700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21963600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21629200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23419200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23992300</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2510800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1849100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1798500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1527000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1568100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1654400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1859500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1956500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1551000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1565400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1654400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1801800</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2850,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60026800</v>
+      </c>
+      <c r="E66" s="3">
         <v>61718400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>59056200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55252200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>56180500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>57532500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>60855800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>66078300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55956400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54475300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57532500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>62211600</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3031,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3072,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>39431300</v>
+      </c>
+      <c r="E72" s="3">
         <v>40216200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>37785400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>31786800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>33268600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>33358400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>31391500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29285500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>31724100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>31338700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>33358400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>32665800</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3236,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41445000</v>
+      </c>
+      <c r="E76" s="3">
         <v>39797200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>38431700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35507200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35879600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>36283100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34581100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29984700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34893900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>35342100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>36283100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>35877800</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,51 +3318,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44286</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3211,8 +3405,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,46 +3424,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>376000</v>
+      </c>
+      <c r="E83" s="3">
         <v>423700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>432700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>532000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>443000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>87100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>75200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>241500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>699900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>733600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>432700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>872800</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3668,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2598500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1701600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1943500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1291600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2326000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2270600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1886900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2690100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1708400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1480400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2270600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1267000</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,46 +3728,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-638000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-387100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-553600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-365500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-710100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-502200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-492500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-442800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-226100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-156300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-502200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-298600</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3849,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-448000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-336200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-237300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-609400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-341900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-125800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-143100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-225000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-279200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-338900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-125800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-987800</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,23 +3909,24 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>983900</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>716300</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -3707,16 +3940,19 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>755700</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>725400</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,118 +4071,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1646700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1460000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1720700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-795200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1906200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1587300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-706100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2834700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1543000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1158500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1587300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-857500</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E101" s="3">
         <v>4100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>181800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>82000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-98300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-137900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>18600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>53000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>123300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>181800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>73800</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>563800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-107100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-88000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-22300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>147400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>561600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1219500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-287700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-74000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>80500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>561600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-691000</v>
       </c>
     </row>
